--- a/latest.xlsx
+++ b/latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박민지\Desktop\★ 구매 업무\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박민지\Desktop\★ 구매 업무\◈ 보고 자료\09. 26년 사업계획\01. 월별 단가 영향 인자\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731B3C77-4A4D-4E9F-B0E9-B460A25D0E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71724D00-734C-4911-BA6F-E9E732C1CD2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="1440" windowWidth="23256" windowHeight="12456" xr2:uid="{4F76B2AE-5DB7-4740-9054-E51EB5634948}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F76B2AE-5DB7-4740-9054-E51EB5634948}"/>
   </bookViews>
   <sheets>
     <sheet name="2026년" sheetId="1" r:id="rId1"/>
@@ -332,7 +332,7 @@
     <numFmt numFmtId="178" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;"/>
     <numFmt numFmtId="179" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,12 +398,6 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -503,50 +497,50 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -917,41 +911,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="14" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="17"/>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="17"/>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
-      <c r="AA2" s="17"/>
-      <c r="AB2" s="17"/>
-      <c r="AC2" s="17" t="s">
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="AD2" s="18">
+      <c r="AD2" s="16">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="3" spans="2:30" x14ac:dyDescent="0.3">
@@ -1059,68 +1053,68 @@
       <c r="F4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="17">
         <v>2574.9499999999998</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="17">
         <v>2653.38</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="17">
         <v>2657.21</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="17">
         <v>2381.25</v>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="17">
         <v>2442.4</v>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="17">
         <v>2516.48</v>
       </c>
-      <c r="M4" s="19">
+      <c r="M4" s="17">
         <v>2604.15</v>
       </c>
-      <c r="N4" s="19">
+      <c r="N4" s="17">
         <v>2594.0300000000002</v>
       </c>
-      <c r="O4" s="19">
+      <c r="O4" s="17">
         <v>2653.25</v>
       </c>
-      <c r="P4" s="19">
+      <c r="P4" s="17">
         <v>2786.3</v>
       </c>
-      <c r="Q4" s="19">
+      <c r="Q4" s="17">
         <v>2822.93</v>
       </c>
-      <c r="R4" s="19">
+      <c r="R4" s="17">
         <v>2875.45</v>
       </c>
-      <c r="S4" s="20">
+      <c r="S4" s="18">
         <v>3148.4</v>
       </c>
-      <c r="T4" s="20">
+      <c r="T4" s="18">
         <v>3065.35</v>
       </c>
-      <c r="U4" s="21">
+      <c r="U4" s="19">
         <v>3370.16</v>
       </c>
-      <c r="V4" s="21">
+      <c r="V4" s="19">
         <v>3600.63</v>
       </c>
-      <c r="W4" s="22">
+      <c r="W4" s="20">
         <v>3670.18</v>
       </c>
-      <c r="X4" s="21">
+      <c r="X4" s="19">
         <v>3458.64</v>
       </c>
-      <c r="Y4" s="23">
-        <v>3131.75</v>
-      </c>
-      <c r="Z4" s="23"/>
-      <c r="AA4" s="23"/>
-      <c r="AB4" s="23"/>
-      <c r="AC4" s="23"/>
-      <c r="AD4" s="23"/>
+      <c r="Y4" s="21">
+        <v>3155.98</v>
+      </c>
+      <c r="Z4" s="21"/>
+      <c r="AA4" s="21"/>
+      <c r="AB4" s="21"/>
+      <c r="AC4" s="21"/>
+      <c r="AD4" s="21"/>
     </row>
     <row r="5" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
@@ -1138,68 +1132,68 @@
       <c r="F5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="17">
         <v>80.41</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="17">
         <v>77.92</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="17">
         <v>72.489999999999995</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="17">
         <v>67.75</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="17">
         <v>63.73</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="17">
         <v>69.260000000000005</v>
       </c>
-      <c r="M5" s="19">
+      <c r="M5" s="17">
         <v>70.87</v>
       </c>
-      <c r="N5" s="19">
+      <c r="N5" s="17">
         <v>69.39</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="17">
         <v>70.010000000000005</v>
       </c>
-      <c r="P5" s="19">
+      <c r="P5" s="17">
         <v>65</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="Q5" s="17">
         <v>64.47</v>
       </c>
-      <c r="R5" s="19">
+      <c r="R5" s="17">
         <v>62.06</v>
       </c>
-      <c r="S5" s="20">
+      <c r="S5" s="18">
         <v>61.97</v>
       </c>
-      <c r="T5" s="20">
+      <c r="T5" s="18">
         <v>68.400000000000006</v>
       </c>
-      <c r="U5" s="21">
+      <c r="U5" s="19">
         <v>128.52000000000001</v>
       </c>
-      <c r="V5" s="21">
+      <c r="V5" s="19">
         <v>105.7</v>
       </c>
-      <c r="W5" s="21">
+      <c r="W5" s="19">
         <v>103.15</v>
       </c>
-      <c r="X5" s="21">
+      <c r="X5" s="19">
         <v>79.45</v>
       </c>
-      <c r="Y5" s="23">
-        <v>71.52</v>
-      </c>
-      <c r="Z5" s="23"/>
-      <c r="AA5" s="23"/>
-      <c r="AB5" s="23"/>
-      <c r="AC5" s="23"/>
-      <c r="AD5" s="23"/>
+      <c r="Y5" s="21">
+        <v>78.209999999999994</v>
+      </c>
+      <c r="Z5" s="21"/>
+      <c r="AA5" s="21"/>
+      <c r="AB5" s="21"/>
+      <c r="AC5" s="21"/>
+      <c r="AD5" s="21"/>
     </row>
     <row r="6" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
@@ -1217,68 +1211,68 @@
       <c r="F6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="17">
         <v>673.8</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="17">
         <v>667.35</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="17">
         <v>638.41</v>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="17">
         <v>575.44000000000005</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="17">
         <v>568.59</v>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="17">
         <v>593.35</v>
       </c>
-      <c r="M6" s="19">
+      <c r="M6" s="17">
         <v>582.85</v>
       </c>
-      <c r="N6" s="19">
+      <c r="N6" s="17">
         <v>579.6</v>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="17">
         <v>603.5</v>
       </c>
-      <c r="P6" s="19">
+      <c r="P6" s="17">
         <v>569.57000000000005</v>
       </c>
-      <c r="Q6" s="19">
+      <c r="Q6" s="17">
         <v>574.6</v>
       </c>
-      <c r="R6" s="19">
+      <c r="R6" s="17">
         <v>549.57000000000005</v>
       </c>
-      <c r="S6" s="20">
+      <c r="S6" s="18">
         <v>557.36</v>
       </c>
-      <c r="T6" s="24">
+      <c r="T6" s="22">
         <v>608.6</v>
       </c>
-      <c r="U6" s="24">
+      <c r="U6" s="22">
         <v>1018.64</v>
       </c>
-      <c r="V6" s="25">
+      <c r="V6" s="23">
         <v>1063.1400000000001</v>
       </c>
-      <c r="W6" s="24">
+      <c r="W6" s="22">
         <v>957.67</v>
       </c>
-      <c r="X6" s="24">
+      <c r="X6" s="22">
         <v>708.41</v>
       </c>
-      <c r="Y6" s="16">
-        <v>725.73</v>
-      </c>
-      <c r="Z6" s="16"/>
-      <c r="AA6" s="16"/>
-      <c r="AB6" s="16"/>
-      <c r="AC6" s="16"/>
-      <c r="AD6" s="16"/>
+      <c r="Y6" s="14">
+        <v>807.13</v>
+      </c>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="14"/>
     </row>
     <row r="7" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
@@ -1296,68 +1290,68 @@
       <c r="F7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="17">
         <v>832</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="17">
         <v>855</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="17">
         <v>828.75</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="17">
         <v>767.5</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="17">
         <v>743</v>
       </c>
-      <c r="L7" s="19">
+      <c r="L7" s="17">
         <v>767.5</v>
       </c>
-      <c r="M7" s="19">
+      <c r="M7" s="17">
         <v>783.75</v>
       </c>
-      <c r="N7" s="19">
+      <c r="N7" s="17">
         <v>785</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="17">
         <v>800</v>
       </c>
-      <c r="P7" s="19">
+      <c r="P7" s="17">
         <v>736</v>
       </c>
-      <c r="Q7" s="19">
+      <c r="Q7" s="17">
         <v>695</v>
       </c>
-      <c r="R7" s="19">
+      <c r="R7" s="17">
         <v>705</v>
       </c>
-      <c r="S7" s="20">
+      <c r="S7" s="18">
         <v>675</v>
       </c>
-      <c r="T7" s="24">
+      <c r="T7" s="22">
         <v>663.75</v>
       </c>
-      <c r="U7" s="24">
+      <c r="U7" s="22">
         <v>1216.25</v>
       </c>
-      <c r="V7" s="25">
+      <c r="V7" s="23">
         <v>1378</v>
       </c>
-      <c r="W7" s="24">
+      <c r="W7" s="22">
         <v>1097.5</v>
       </c>
-      <c r="X7" s="24">
+      <c r="X7" s="22">
         <v>843.75</v>
       </c>
-      <c r="Y7" s="16">
-        <v>823.33</v>
-      </c>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="16"/>
-      <c r="AB7" s="16"/>
-      <c r="AC7" s="16"/>
-      <c r="AD7" s="16"/>
+      <c r="Y7" s="14">
+        <v>876</v>
+      </c>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14"/>
     </row>
     <row r="8" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
@@ -1375,66 +1369,68 @@
       <c r="F8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="17">
         <v>172.56</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="17">
         <v>172.56</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="17">
         <v>172.56</v>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="17">
         <v>172.56</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="17">
         <v>172.56</v>
       </c>
-      <c r="L8" s="19">
+      <c r="L8" s="17">
         <v>172.56</v>
       </c>
-      <c r="M8" s="19">
+      <c r="M8" s="17">
         <v>172.56</v>
       </c>
-      <c r="N8" s="19">
+      <c r="N8" s="17">
         <v>172.56</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="17">
         <v>172.56</v>
       </c>
-      <c r="P8" s="19">
+      <c r="P8" s="17">
         <v>172.56</v>
       </c>
-      <c r="Q8" s="19">
+      <c r="Q8" s="17">
         <v>172.56</v>
       </c>
-      <c r="R8" s="19">
+      <c r="R8" s="17">
         <v>172.56</v>
       </c>
-      <c r="S8" s="20">
+      <c r="S8" s="18">
         <v>169.61</v>
       </c>
-      <c r="T8" s="20">
+      <c r="T8" s="18">
         <v>169.1</v>
       </c>
-      <c r="U8" s="20">
+      <c r="U8" s="18">
         <v>177.96</v>
       </c>
-      <c r="V8" s="22">
+      <c r="V8" s="20">
         <v>178.12</v>
       </c>
-      <c r="W8" s="20">
+      <c r="W8" s="18">
         <v>181.63</v>
       </c>
-      <c r="X8" s="20">
+      <c r="X8" s="18">
         <v>166.12</v>
       </c>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
-      <c r="AA8" s="16"/>
-      <c r="AB8" s="16"/>
-      <c r="AC8" s="16"/>
-      <c r="AD8" s="16"/>
+      <c r="Y8" s="14">
+        <v>174.89</v>
+      </c>
+      <c r="Z8" s="14"/>
+      <c r="AA8" s="14"/>
+      <c r="AB8" s="14"/>
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="14"/>
     </row>
     <row r="9" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
@@ -1452,66 +1448,68 @@
       <c r="F9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="17">
         <v>665</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="17">
         <v>705</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="17">
         <v>730</v>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="24">
         <v>750</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="17">
         <v>675</v>
       </c>
-      <c r="L9" s="19">
+      <c r="L9" s="17">
         <v>645</v>
       </c>
-      <c r="M9" s="19">
+      <c r="M9" s="17">
         <v>645</v>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="17">
         <v>630</v>
       </c>
-      <c r="O9" s="19">
+      <c r="O9" s="17">
         <v>650</v>
       </c>
-      <c r="P9" s="19">
+      <c r="P9" s="17">
         <v>660</v>
       </c>
-      <c r="Q9" s="19">
+      <c r="Q9" s="17">
         <v>670</v>
       </c>
-      <c r="R9" s="19">
+      <c r="R9" s="17">
         <v>675</v>
       </c>
-      <c r="S9" s="20">
+      <c r="S9" s="18">
         <v>700</v>
       </c>
-      <c r="T9" s="20">
+      <c r="T9" s="18">
         <v>740</v>
       </c>
-      <c r="U9" s="21">
+      <c r="U9" s="19">
         <v>760</v>
       </c>
-      <c r="V9" s="21">
+      <c r="V9" s="19">
         <v>780</v>
       </c>
-      <c r="W9" s="21">
+      <c r="W9" s="19">
         <v>780</v>
       </c>
-      <c r="X9" s="21">
+      <c r="X9" s="19">
         <v>780</v>
       </c>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="23"/>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="23"/>
-      <c r="AC9" s="23"/>
-      <c r="AD9" s="23"/>
+      <c r="Y9" s="21">
+        <v>760</v>
+      </c>
+      <c r="Z9" s="21"/>
+      <c r="AA9" s="21"/>
+      <c r="AB9" s="21"/>
+      <c r="AC9" s="21"/>
+      <c r="AD9" s="21"/>
     </row>
     <row r="10" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
@@ -1529,279 +1527,287 @@
       <c r="F10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="17">
         <v>105.1</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="17">
         <v>91</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="17">
         <v>80</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="17">
         <v>81.3</v>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="17">
         <v>81.900000000000006</v>
       </c>
-      <c r="L10" s="26">
+      <c r="L10" s="24">
         <v>88.7</v>
       </c>
-      <c r="M10" s="19">
+      <c r="M10" s="17">
         <v>90.3</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="17">
         <v>90.5</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="17">
         <v>90.8</v>
       </c>
-      <c r="P10" s="19">
+      <c r="P10" s="17">
         <v>89.5</v>
       </c>
-      <c r="Q10" s="19">
+      <c r="Q10" s="17">
         <v>89.5</v>
       </c>
-      <c r="R10" s="19">
+      <c r="R10" s="17">
         <v>81.7</v>
       </c>
-      <c r="S10" s="20">
+      <c r="S10" s="18">
         <v>81.599999999999994</v>
       </c>
-      <c r="T10" s="20">
+      <c r="T10" s="18">
         <v>82.5</v>
       </c>
-      <c r="U10" s="21">
+      <c r="U10" s="19">
         <v>81.5</v>
       </c>
-      <c r="V10" s="21">
+      <c r="V10" s="19">
         <v>81.099999999999994</v>
       </c>
-      <c r="W10" s="21">
+      <c r="W10" s="19">
         <v>81.2</v>
       </c>
-      <c r="X10" s="21">
+      <c r="X10" s="19">
         <v>81.5</v>
       </c>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="23"/>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="23"/>
-      <c r="AC10" s="23"/>
-      <c r="AD10" s="23"/>
+      <c r="Y10" s="21">
+        <v>83.8</v>
+      </c>
+      <c r="Z10" s="21"/>
+      <c r="AA10" s="21"/>
+      <c r="AB10" s="21"/>
+      <c r="AC10" s="21"/>
+      <c r="AD10" s="21"/>
     </row>
     <row r="11" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B11" s="27">
+      <c r="B11" s="25">
         <v>8</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16">
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14">
         <v>1455.79</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="14">
         <v>1445.56</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="14">
         <v>1456.95</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="14">
         <v>1444.31</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="14">
         <v>1394.49</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="14">
         <v>1366.95</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="14">
         <v>1375.22</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="14">
         <v>1389.66</v>
       </c>
-      <c r="O11" s="16">
+      <c r="O11" s="14">
         <v>1391.83</v>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="14">
         <v>1423.36</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="14">
         <v>1457.77</v>
       </c>
-      <c r="R11" s="16">
+      <c r="R11" s="14">
         <v>1467.4</v>
       </c>
-      <c r="S11" s="28">
+      <c r="S11" s="26">
         <v>1456.51</v>
       </c>
-      <c r="T11" s="28">
+      <c r="T11" s="26">
         <v>1449.32</v>
       </c>
-      <c r="U11" s="28">
+      <c r="U11" s="26">
         <v>1486.64</v>
       </c>
-      <c r="V11" s="28">
+      <c r="V11" s="26">
         <v>1487.39</v>
       </c>
-      <c r="W11" s="28">
+      <c r="W11" s="26">
         <v>1490.11</v>
       </c>
-      <c r="X11" s="20">
+      <c r="X11" s="18">
         <v>1527.3</v>
       </c>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="16"/>
-      <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
-      <c r="AD11" s="16"/>
+      <c r="Y11" s="14">
+        <v>1441.1</v>
+      </c>
+      <c r="Z11" s="14"/>
+      <c r="AA11" s="14"/>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="14"/>
+      <c r="AD11" s="14"/>
     </row>
     <row r="12" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B12" s="27">
+      <c r="B12" s="25">
         <v>9</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16">
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14">
         <v>1504.11</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="14">
         <v>1505.44</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="14">
         <v>1575.91</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="14">
         <v>1617.71</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="14">
         <v>1571.45</v>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="14">
         <v>1574.56</v>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="14">
         <v>1607.95</v>
       </c>
-      <c r="N12" s="16">
+      <c r="N12" s="14">
         <v>1617.03</v>
       </c>
-      <c r="O12" s="16">
+      <c r="O12" s="14">
         <v>1633.09</v>
       </c>
-      <c r="P12" s="16">
+      <c r="P12" s="14">
         <v>1655.73</v>
       </c>
-      <c r="Q12" s="16">
+      <c r="Q12" s="14">
         <v>1684.9</v>
       </c>
-      <c r="R12" s="16">
+      <c r="R12" s="14">
         <v>1717.96</v>
       </c>
-      <c r="S12" s="28">
+      <c r="S12" s="26">
         <v>1709.82</v>
       </c>
-      <c r="T12" s="28">
+      <c r="T12" s="26">
         <v>1709.82</v>
       </c>
-      <c r="U12" s="28">
+      <c r="U12" s="26">
         <v>1713.05</v>
       </c>
-      <c r="V12" s="28">
+      <c r="V12" s="26">
         <v>1718.26</v>
       </c>
-      <c r="W12" s="28">
+      <c r="W12" s="26">
         <v>1737.95</v>
       </c>
-      <c r="X12" s="20">
+      <c r="X12" s="18">
         <v>1758.45</v>
       </c>
-      <c r="Y12" s="16"/>
-      <c r="Z12" s="16"/>
-      <c r="AA12" s="16"/>
-      <c r="AB12" s="16"/>
-      <c r="AC12" s="16"/>
-      <c r="AD12" s="16"/>
+      <c r="Y12" s="14">
+        <v>1709.78</v>
+      </c>
+      <c r="Z12" s="14"/>
+      <c r="AA12" s="14"/>
+      <c r="AB12" s="14"/>
+      <c r="AC12" s="14"/>
+      <c r="AD12" s="14"/>
     </row>
     <row r="13" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B13" s="27">
+      <c r="B13" s="25">
         <v>10</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16">
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14">
         <v>927.97</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="14">
         <v>952.59</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="14">
         <v>977.77</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="14">
         <v>999.96</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="14">
         <v>962.28</v>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="14">
         <v>944.94</v>
       </c>
-      <c r="M13" s="16">
+      <c r="M13" s="14">
         <v>936.97</v>
       </c>
-      <c r="N13" s="16">
+      <c r="N13" s="14">
         <v>941.32</v>
       </c>
-      <c r="O13" s="16">
+      <c r="O13" s="14">
         <v>941.2</v>
       </c>
-      <c r="P13" s="16">
+      <c r="P13" s="14">
         <v>939.16</v>
       </c>
-      <c r="Q13" s="16">
+      <c r="Q13" s="14">
         <v>939.83</v>
       </c>
-      <c r="R13" s="16">
+      <c r="R13" s="14">
         <v>941.39</v>
       </c>
-      <c r="S13" s="28">
+      <c r="S13" s="26">
         <v>929.51</v>
       </c>
-      <c r="T13" s="28">
+      <c r="T13" s="26">
         <v>932.63</v>
       </c>
-      <c r="U13" s="28">
+      <c r="U13" s="26">
         <v>936.68</v>
       </c>
-      <c r="V13" s="28">
+      <c r="V13" s="26">
         <v>933.92</v>
       </c>
-      <c r="W13" s="28">
+      <c r="W13" s="26">
         <v>942.04</v>
       </c>
-      <c r="X13" s="28">
+      <c r="X13" s="26">
         <v>950.38</v>
       </c>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="16"/>
-      <c r="AB13" s="16"/>
-      <c r="AC13" s="16"/>
-      <c r="AD13" s="16"/>
+      <c r="Y13" s="14">
+        <v>921.46</v>
+      </c>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="14"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2067,10 +2073,10 @@
       <c r="E13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="14"/>
+      <c r="G13" s="27"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
@@ -2085,10 +2091,10 @@
         <v>57</v>
       </c>
       <c r="E14" s="6"/>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="G14" s="15"/>
+      <c r="G14" s="28"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
@@ -2101,10 +2107,10 @@
         <v>57</v>
       </c>
       <c r="E15" s="6"/>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="28"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
@@ -2119,10 +2125,10 @@
       <c r="E16" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="G16" s="15"/>
+      <c r="G16" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박민지\Desktop\★ 구매 업무\◈ 보고 자료\09. 26년 사업계획\01. 월별 단가 영향 인자\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71724D00-734C-4911-BA6F-E9E732C1CD2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53687823-A809-4205-82E1-A597D9BC0533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F76B2AE-5DB7-4740-9054-E51EB5634948}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="82">
   <si>
     <t>알루미늄</t>
   </si>
@@ -124,84 +124,72 @@
     <t>BE</t>
   </si>
   <si>
+    <t>알코올</t>
+  </si>
+  <si>
+    <t>세일즈팩</t>
+  </si>
+  <si>
+    <t>박스류</t>
+  </si>
+  <si>
+    <t>KRW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>kg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>두바이유</t>
+  </si>
+  <si>
+    <t>나프타</t>
+  </si>
+  <si>
+    <t>에틸렌</t>
+  </si>
+  <si>
+    <t>no.</t>
+  </si>
+  <si>
+    <t>원료항목</t>
+  </si>
+  <si>
+    <t>관련 구매품</t>
+  </si>
+  <si>
+    <t>통화</t>
+  </si>
+  <si>
+    <t>단위</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>ton</t>
+  </si>
+  <si>
+    <t>bbl</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
     <t>옥수수(종가 기준)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>알코올</t>
   </si>
   <si>
     <t>펄프(월 말 업데이트)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>세일즈팩</t>
   </si>
   <si>
     <t>폐골판지(월 말 업데이트)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>박스류</t>
   </si>
   <si>
     <t>KRW</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>kg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>두바이유</t>
-  </si>
-  <si>
-    <t>나프타</t>
-  </si>
-  <si>
-    <t>에틸렌</t>
-  </si>
-  <si>
-    <t>no.</t>
-  </si>
-  <si>
-    <t>원료항목</t>
-  </si>
-  <si>
-    <t>관련 구매품</t>
-  </si>
-  <si>
-    <t>통화</t>
-  </si>
-  <si>
-    <t>단위</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>ton</t>
-  </si>
-  <si>
-    <t>bbl</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>옥수수(종가 기준)</t>
-  </si>
-  <si>
-    <t>펄프(월 말 업데이트)</t>
-  </si>
-  <si>
-    <t>폐골판지(월 말 업데이트)</t>
-  </si>
-  <si>
-    <t>KRW</t>
-  </si>
-  <si>
-    <t>kg</t>
   </si>
   <si>
     <t xml:space="preserve">▶ 원자재 </t>
@@ -318,6 +306,30 @@
   </si>
   <si>
     <t>2025년</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>월 말 업데이트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>종가 기준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥수수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>펄프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐골판지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026년</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -454,7 +466,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -503,9 +515,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -540,6 +549,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -897,63 +912,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37802FCA-6AA8-48C0-AEEF-F959BD03128C}">
-  <dimension ref="B2:AD13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AD13"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.625" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="5.25" customWidth="1"/>
     <col min="3" max="3" width="24.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="15" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="27" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="15" width="11.875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="18" width="13.125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="11.875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="20" max="27" width="11.875" bestFit="1" customWidth="1"/>
     <col min="28" max="30" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="C1" s="28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="C2" s="29">
+        <f ca="1">TODAY()</f>
+        <v>46238</v>
+      </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="15"/>
-      <c r="G2" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD2" s="16">
-        <f ca="1">TODAY()</f>
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="3" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="G2" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="26"/>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>3</v>
@@ -965,40 +985,40 @@
         <v>5</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="S3" s="7">
         <v>46023</v>
@@ -1037,7 +1057,7 @@
         <v>46357</v>
       </c>
     </row>
-    <row r="4" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B4" s="3">
         <v>1</v>
       </c>
@@ -1053,70 +1073,70 @@
       <c r="F4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="16">
         <v>2574.9499999999998</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="16">
         <v>2653.38</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="16">
         <v>2657.21</v>
       </c>
-      <c r="J4" s="17">
+      <c r="J4" s="16">
         <v>2381.25</v>
       </c>
-      <c r="K4" s="17">
+      <c r="K4" s="16">
         <v>2442.4</v>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="16">
         <v>2516.48</v>
       </c>
-      <c r="M4" s="17">
+      <c r="M4" s="16">
         <v>2604.15</v>
       </c>
-      <c r="N4" s="17">
+      <c r="N4" s="16">
         <v>2594.0300000000002</v>
       </c>
-      <c r="O4" s="17">
+      <c r="O4" s="16">
         <v>2653.25</v>
       </c>
-      <c r="P4" s="17">
+      <c r="P4" s="16">
         <v>2786.3</v>
       </c>
-      <c r="Q4" s="17">
+      <c r="Q4" s="16">
         <v>2822.93</v>
       </c>
-      <c r="R4" s="17">
+      <c r="R4" s="16">
         <v>2875.45</v>
       </c>
-      <c r="S4" s="18">
+      <c r="S4" s="17">
         <v>3148.4</v>
       </c>
-      <c r="T4" s="18">
+      <c r="T4" s="17">
         <v>3065.35</v>
       </c>
-      <c r="U4" s="19">
+      <c r="U4" s="18">
         <v>3370.16</v>
       </c>
-      <c r="V4" s="19">
+      <c r="V4" s="18">
         <v>3600.63</v>
       </c>
-      <c r="W4" s="20">
+      <c r="W4" s="19">
         <v>3670.18</v>
       </c>
-      <c r="X4" s="19">
+      <c r="X4" s="18">
         <v>3458.64</v>
       </c>
-      <c r="Y4" s="21">
+      <c r="Y4" s="20">
         <v>3155.98</v>
       </c>
-      <c r="Z4" s="21"/>
-      <c r="AA4" s="21"/>
-      <c r="AB4" s="21"/>
-      <c r="AC4" s="21"/>
-      <c r="AD4" s="21"/>
-    </row>
-    <row r="5" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="20"/>
+      <c r="AB4" s="20"/>
+      <c r="AC4" s="20"/>
+      <c r="AD4" s="20"/>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
         <v>2</v>
       </c>
@@ -1132,70 +1152,70 @@
       <c r="F5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="16">
         <v>80.41</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="16">
         <v>77.92</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="16">
         <v>72.489999999999995</v>
       </c>
-      <c r="J5" s="17">
+      <c r="J5" s="16">
         <v>67.75</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="16">
         <v>63.73</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="16">
         <v>69.260000000000005</v>
       </c>
-      <c r="M5" s="17">
+      <c r="M5" s="16">
         <v>70.87</v>
       </c>
-      <c r="N5" s="17">
+      <c r="N5" s="16">
         <v>69.39</v>
       </c>
-      <c r="O5" s="17">
+      <c r="O5" s="16">
         <v>70.010000000000005</v>
       </c>
-      <c r="P5" s="17">
+      <c r="P5" s="16">
         <v>65</v>
       </c>
-      <c r="Q5" s="17">
+      <c r="Q5" s="16">
         <v>64.47</v>
       </c>
-      <c r="R5" s="17">
+      <c r="R5" s="16">
         <v>62.06</v>
       </c>
-      <c r="S5" s="18">
+      <c r="S5" s="17">
         <v>61.97</v>
       </c>
-      <c r="T5" s="18">
+      <c r="T5" s="17">
         <v>68.400000000000006</v>
       </c>
-      <c r="U5" s="19">
+      <c r="U5" s="18">
         <v>128.52000000000001</v>
       </c>
-      <c r="V5" s="19">
+      <c r="V5" s="18">
         <v>105.7</v>
       </c>
-      <c r="W5" s="19">
+      <c r="W5" s="18">
         <v>103.15</v>
       </c>
-      <c r="X5" s="19">
+      <c r="X5" s="18">
         <v>79.45</v>
       </c>
-      <c r="Y5" s="21">
+      <c r="Y5" s="20">
         <v>78.209999999999994</v>
       </c>
-      <c r="Z5" s="21"/>
-      <c r="AA5" s="21"/>
-      <c r="AB5" s="21"/>
-      <c r="AC5" s="21"/>
-      <c r="AD5" s="21"/>
-    </row>
-    <row r="6" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="20"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>3</v>
       </c>
@@ -1211,58 +1231,58 @@
       <c r="F6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="16">
         <v>673.8</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="16">
         <v>667.35</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="16">
         <v>638.41</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="16">
         <v>575.44000000000005</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="16">
         <v>568.59</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="16">
         <v>593.35</v>
       </c>
-      <c r="M6" s="17">
+      <c r="M6" s="16">
         <v>582.85</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="16">
         <v>579.6</v>
       </c>
-      <c r="O6" s="17">
+      <c r="O6" s="16">
         <v>603.5</v>
       </c>
-      <c r="P6" s="17">
+      <c r="P6" s="16">
         <v>569.57000000000005</v>
       </c>
-      <c r="Q6" s="17">
+      <c r="Q6" s="16">
         <v>574.6</v>
       </c>
-      <c r="R6" s="17">
+      <c r="R6" s="16">
         <v>549.57000000000005</v>
       </c>
-      <c r="S6" s="18">
+      <c r="S6" s="17">
         <v>557.36</v>
       </c>
-      <c r="T6" s="22">
+      <c r="T6" s="21">
         <v>608.6</v>
       </c>
-      <c r="U6" s="22">
+      <c r="U6" s="21">
         <v>1018.64</v>
       </c>
-      <c r="V6" s="23">
+      <c r="V6" s="22">
         <v>1063.1400000000001</v>
       </c>
-      <c r="W6" s="22">
+      <c r="W6" s="21">
         <v>957.67</v>
       </c>
-      <c r="X6" s="22">
+      <c r="X6" s="21">
         <v>708.41</v>
       </c>
       <c r="Y6" s="14">
@@ -1274,7 +1294,7 @@
       <c r="AC6" s="14"/>
       <c r="AD6" s="14"/>
     </row>
-    <row r="7" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>4</v>
       </c>
@@ -1290,58 +1310,58 @@
       <c r="F7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="16">
         <v>832</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="16">
         <v>855</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="16">
         <v>828.75</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="16">
         <v>767.5</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="16">
         <v>743</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="16">
         <v>767.5</v>
       </c>
-      <c r="M7" s="17">
+      <c r="M7" s="16">
         <v>783.75</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="16">
         <v>785</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="16">
         <v>800</v>
       </c>
-      <c r="P7" s="17">
+      <c r="P7" s="16">
         <v>736</v>
       </c>
-      <c r="Q7" s="17">
+      <c r="Q7" s="16">
         <v>695</v>
       </c>
-      <c r="R7" s="17">
+      <c r="R7" s="16">
         <v>705</v>
       </c>
-      <c r="S7" s="18">
+      <c r="S7" s="17">
         <v>675</v>
       </c>
-      <c r="T7" s="22">
+      <c r="T7" s="21">
         <v>663.75</v>
       </c>
-      <c r="U7" s="22">
+      <c r="U7" s="21">
         <v>1216.25</v>
       </c>
-      <c r="V7" s="23">
+      <c r="V7" s="22">
         <v>1378</v>
       </c>
-      <c r="W7" s="22">
+      <c r="W7" s="21">
         <v>1097.5</v>
       </c>
-      <c r="X7" s="22">
+      <c r="X7" s="21">
         <v>843.75</v>
       </c>
       <c r="Y7" s="14">
@@ -1353,15 +1373,18 @@
       <c r="AC7" s="14"/>
       <c r="AD7" s="14"/>
     </row>
-    <row r="8" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
       <c r="B8" s="3">
         <v>5</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>7</v>
@@ -1369,58 +1392,58 @@
       <c r="F8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="16">
         <v>172.56</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="16">
         <v>172.56</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="16">
         <v>172.56</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="16">
         <v>172.56</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="16">
         <v>172.56</v>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="16">
         <v>172.56</v>
       </c>
-      <c r="M8" s="17">
+      <c r="M8" s="16">
         <v>172.56</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="16">
         <v>172.56</v>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="16">
         <v>172.56</v>
       </c>
-      <c r="P8" s="17">
+      <c r="P8" s="16">
         <v>172.56</v>
       </c>
-      <c r="Q8" s="17">
+      <c r="Q8" s="16">
         <v>172.56</v>
       </c>
-      <c r="R8" s="17">
+      <c r="R8" s="16">
         <v>172.56</v>
       </c>
-      <c r="S8" s="18">
+      <c r="S8" s="17">
         <v>169.61</v>
       </c>
-      <c r="T8" s="18">
+      <c r="T8" s="17">
         <v>169.1</v>
       </c>
-      <c r="U8" s="18">
+      <c r="U8" s="17">
         <v>177.96</v>
       </c>
-      <c r="V8" s="20">
+      <c r="V8" s="19">
         <v>178.12</v>
       </c>
-      <c r="W8" s="18">
+      <c r="W8" s="17">
         <v>181.63</v>
       </c>
-      <c r="X8" s="18">
+      <c r="X8" s="17">
         <v>166.12</v>
       </c>
       <c r="Y8" s="14">
@@ -1432,15 +1455,18 @@
       <c r="AC8" s="14"/>
       <c r="AD8" s="14"/>
     </row>
-    <row r="9" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>76</v>
+      </c>
       <c r="B9" s="3">
         <v>6</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>7</v>
@@ -1448,150 +1474,153 @@
       <c r="F9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="16">
         <v>665</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="16">
         <v>705</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="16">
         <v>730</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="23">
         <v>750</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="16">
         <v>675</v>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="16">
         <v>645</v>
       </c>
-      <c r="M9" s="17">
+      <c r="M9" s="16">
         <v>645</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="16">
         <v>630</v>
       </c>
-      <c r="O9" s="17">
+      <c r="O9" s="16">
         <v>650</v>
       </c>
-      <c r="P9" s="17">
+      <c r="P9" s="16">
         <v>660</v>
       </c>
-      <c r="Q9" s="17">
+      <c r="Q9" s="16">
         <v>670</v>
       </c>
-      <c r="R9" s="17">
+      <c r="R9" s="16">
         <v>675</v>
       </c>
-      <c r="S9" s="18">
+      <c r="S9" s="17">
         <v>700</v>
       </c>
-      <c r="T9" s="18">
+      <c r="T9" s="17">
         <v>740</v>
       </c>
-      <c r="U9" s="19">
+      <c r="U9" s="18">
         <v>760</v>
       </c>
-      <c r="V9" s="19">
+      <c r="V9" s="18">
         <v>780</v>
       </c>
-      <c r="W9" s="19">
+      <c r="W9" s="18">
         <v>780</v>
       </c>
-      <c r="X9" s="19">
+      <c r="X9" s="18">
         <v>780</v>
       </c>
-      <c r="Y9" s="21">
+      <c r="Y9" s="20">
         <v>760</v>
       </c>
-      <c r="Z9" s="21"/>
-      <c r="AA9" s="21"/>
-      <c r="AB9" s="21"/>
-      <c r="AC9" s="21"/>
-      <c r="AD9" s="21"/>
-    </row>
-    <row r="10" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="20"/>
+      <c r="AD9" s="20"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
       <c r="B10" s="3">
         <v>7</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="17">
+      <c r="G10" s="16">
         <v>105.1</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="16">
         <v>91</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="16">
         <v>80</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="16">
         <v>81.3</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="16">
         <v>81.900000000000006</v>
       </c>
-      <c r="L10" s="24">
+      <c r="L10" s="23">
         <v>88.7</v>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="16">
         <v>90.3</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="16">
         <v>90.5</v>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="16">
         <v>90.8</v>
       </c>
-      <c r="P10" s="17">
+      <c r="P10" s="16">
         <v>89.5</v>
       </c>
-      <c r="Q10" s="17">
+      <c r="Q10" s="16">
         <v>89.5</v>
       </c>
-      <c r="R10" s="17">
+      <c r="R10" s="16">
         <v>81.7</v>
       </c>
-      <c r="S10" s="18">
+      <c r="S10" s="17">
         <v>81.599999999999994</v>
       </c>
-      <c r="T10" s="18">
+      <c r="T10" s="17">
         <v>82.5</v>
       </c>
-      <c r="U10" s="19">
+      <c r="U10" s="18">
         <v>81.5</v>
       </c>
-      <c r="V10" s="19">
+      <c r="V10" s="18">
         <v>81.099999999999994</v>
       </c>
-      <c r="W10" s="19">
+      <c r="W10" s="18">
         <v>81.2</v>
       </c>
-      <c r="X10" s="19">
+      <c r="X10" s="18">
         <v>81.5</v>
       </c>
-      <c r="Y10" s="21">
+      <c r="Y10" s="20">
         <v>83.8</v>
       </c>
-      <c r="Z10" s="21"/>
-      <c r="AA10" s="21"/>
-      <c r="AB10" s="21"/>
-      <c r="AC10" s="21"/>
-      <c r="AD10" s="21"/>
-    </row>
-    <row r="11" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B11" s="25">
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="20"/>
+      <c r="AD10" s="20"/>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B11" s="24">
         <v>8</v>
       </c>
       <c r="C11" s="13" t="s">
@@ -1636,22 +1665,22 @@
       <c r="R11" s="14">
         <v>1467.4</v>
       </c>
-      <c r="S11" s="26">
+      <c r="S11" s="25">
         <v>1456.51</v>
       </c>
-      <c r="T11" s="26">
+      <c r="T11" s="25">
         <v>1449.32</v>
       </c>
-      <c r="U11" s="26">
+      <c r="U11" s="25">
         <v>1486.64</v>
       </c>
-      <c r="V11" s="26">
+      <c r="V11" s="25">
         <v>1487.39</v>
       </c>
-      <c r="W11" s="26">
+      <c r="W11" s="25">
         <v>1490.11</v>
       </c>
-      <c r="X11" s="18">
+      <c r="X11" s="17">
         <v>1527.3</v>
       </c>
       <c r="Y11" s="14">
@@ -1663,12 +1692,12 @@
       <c r="AC11" s="14"/>
       <c r="AD11" s="14"/>
     </row>
-    <row r="12" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B12" s="25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B12" s="24">
         <v>9</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
@@ -1709,22 +1738,22 @@
       <c r="R12" s="14">
         <v>1717.96</v>
       </c>
-      <c r="S12" s="26">
+      <c r="S12" s="25">
         <v>1709.82</v>
       </c>
-      <c r="T12" s="26">
+      <c r="T12" s="25">
         <v>1709.82</v>
       </c>
-      <c r="U12" s="26">
+      <c r="U12" s="25">
         <v>1713.05</v>
       </c>
-      <c r="V12" s="26">
+      <c r="V12" s="25">
         <v>1718.26</v>
       </c>
-      <c r="W12" s="26">
+      <c r="W12" s="25">
         <v>1737.95</v>
       </c>
-      <c r="X12" s="18">
+      <c r="X12" s="17">
         <v>1758.45</v>
       </c>
       <c r="Y12" s="14">
@@ -1736,12 +1765,12 @@
       <c r="AC12" s="14"/>
       <c r="AD12" s="14"/>
     </row>
-    <row r="13" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B13" s="25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B13" s="24">
         <v>10</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
@@ -1782,22 +1811,22 @@
       <c r="R13" s="14">
         <v>941.39</v>
       </c>
-      <c r="S13" s="26">
+      <c r="S13" s="25">
         <v>929.51</v>
       </c>
-      <c r="T13" s="26">
+      <c r="T13" s="25">
         <v>932.63</v>
       </c>
-      <c r="U13" s="26">
+      <c r="U13" s="25">
         <v>936.68</v>
       </c>
-      <c r="V13" s="26">
+      <c r="V13" s="25">
         <v>933.92</v>
       </c>
-      <c r="W13" s="26">
+      <c r="W13" s="25">
         <v>942.04</v>
       </c>
-      <c r="X13" s="26">
+      <c r="X13" s="25">
         <v>950.38</v>
       </c>
       <c r="Y13" s="14">
@@ -1810,8 +1839,9 @@
       <c r="AD13" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="G2:R2"/>
+    <mergeCell ref="S2:AD2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1835,33 +1865,33 @@
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
@@ -1875,19 +1905,19 @@
         <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -1895,25 +1925,25 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -1921,25 +1951,25 @@
         <v>3</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="G6" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -1947,25 +1977,25 @@
         <v>4</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="G7" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
@@ -1973,25 +2003,25 @@
         <v>5</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
@@ -1999,25 +2029,25 @@
         <v>6</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
@@ -2025,25 +2055,25 @@
         <v>7</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
@@ -2054,7 +2084,7 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="10"/>
@@ -2062,21 +2092,21 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="27"/>
+        <v>52</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="26"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
@@ -2085,50 +2115,50 @@
         <v>1</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E14" s="6"/>
-      <c r="F14" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" s="28"/>
+      <c r="F14" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="27"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>2</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E15" s="6"/>
-      <c r="F15" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" s="28"/>
+      <c r="F15" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="27"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>3</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="G16" s="28"/>
+      <c r="F16" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="4">
